--- a/Assets/LingBoCanteen/Datatables/Excel/Scene.xlsx
+++ b/Assets/LingBoCanteen/Datatables/Excel/Scene.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\GoldenDolphin\Assets\LingBoCanteen\1_Datatables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\project\GoldenDolphin\GoldenDolphin\GoldenDolphinGame\Assets\LingBoCanteen\Datatables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C36157F-E5F3-4069-AF0C-5596AA106C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133BBE66-5A9F-4C07-B756-B8AA63AAC84C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="3270" windowWidth="12840" windowHeight="7480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,10 +35,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -51,10 +47,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AssetName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BackgroundMusicId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -68,6 +60,30 @@
   </si>
   <si>
     <t>背景音乐编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneAssetName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Menu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -397,14 +413,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -416,77 +433,85 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -494,7 +519,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -502,7 +527,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
